--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="45">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
   <si>
-    <t>Okres: 26.01.2026 (pon.) - 01.02.2026 (niedz.)</t>
+    <t>Okres: 30.03.2026 (pon.) - 05.04.2026 (niedz.)</t>
   </si>
   <si>
     <t>Przeniesiono z</t>
@@ -47,124 +47,112 @@
     <t>Uwagi</t>
   </si>
   <si>
-    <t>26.01.2026, 8, 14:05-14:50, sala: 19</t>
-  </si>
-  <si>
-    <t>26.01.2026, 3, 09:40-10:25, sala: 19</t>
-  </si>
-  <si>
-    <t>Zaleska Magdalena</t>
+    <t>30.03.2026, 10, 15:45-16:30, sala: 22</t>
+  </si>
+  <si>
+    <t>30.03.2026, 8, 14:05-14:50, sala: 27</t>
+  </si>
+  <si>
+    <t>Mocarski Arkadiusz</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3FA</t>
-  </si>
-  <si>
-    <t>Historia</t>
+    <t>1CA</t>
+  </si>
+  <si>
+    <t>Technologie produkcji cukierniczej</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>26.01.2026, 10, 15:45-16:30, sala: 31</t>
-  </si>
-  <si>
-    <t>26.01.2026, 6, 12:25-13:10, sala: 27</t>
-  </si>
-  <si>
-    <t>Kończyńska Małgorzata</t>
+    <t>31.03.2026, 7, 13:15-14:00, sala: 34</t>
+  </si>
+  <si>
+    <t>31.03.2026, 2, 08:50-09:35, sala: 31</t>
+  </si>
+  <si>
+    <t>Nowak Magdalena</t>
+  </si>
+  <si>
+    <t>5TF</t>
+  </si>
+  <si>
+    <t>Matematyka</t>
+  </si>
+  <si>
+    <t>31.03.2026, 2, 08:50-09:35, sala: 28</t>
+  </si>
+  <si>
+    <t>31.03.2026, 2, 08:50-09:35, sala: prs</t>
+  </si>
+  <si>
+    <t>Świerzewicz Katarzyna</t>
+  </si>
+  <si>
+    <t>3K</t>
+  </si>
+  <si>
+    <t>Technika w produkcji gastronomicznej</t>
+  </si>
+  <si>
+    <t>31.03.2026, 3, 09:40-10:25, sala: 29</t>
+  </si>
+  <si>
+    <t>31.03.2026, 3, 09:40-10:25, sala: prs</t>
+  </si>
+  <si>
+    <t>Technologia gastronomiczna z towaroznawstwem</t>
+  </si>
+  <si>
+    <t>31.03.2026, 4, 10:35-11:20, sala: 29</t>
+  </si>
+  <si>
+    <t>31.03.2026, 4, 10:35-11:20, sala: prs</t>
+  </si>
+  <si>
+    <t>31.03.2026, 5, 11:25-12:10, sala: 29</t>
+  </si>
+  <si>
+    <t>31.03.2026, 5, 11:25-12:10, sala: prs</t>
+  </si>
+  <si>
+    <t>Zajęcia z wychowawcą</t>
+  </si>
+  <si>
+    <t>31.03.2026, 11, 16:35-17:20, sala: 34</t>
   </si>
   <si>
     <t>2CB</t>
   </si>
   <si>
-    <t>Rozwój kompetencji zawodowych - dekoracje w cukiernictwie</t>
-  </si>
-  <si>
-    <t>p. Kończyńska, RKZ za lekcję 10</t>
-  </si>
-  <si>
-    <t>26.01.2026, 7, 13:15-14:00, sala: 40</t>
-  </si>
-  <si>
-    <t>26.01.2026, 6, 12:25-13:10, sala: 40</t>
-  </si>
-  <si>
-    <t>Socha Dariusz</t>
-  </si>
-  <si>
-    <t>2TH</t>
-  </si>
-  <si>
-    <t>Obsługa klientów</t>
-  </si>
-  <si>
-    <t>27.01.2026, 13, 18:15-19:00, sala: 34</t>
-  </si>
-  <si>
-    <t>27.01.2026, 11, 16:35-17:20, sala: 34</t>
-  </si>
-  <si>
-    <t>Nowak Magdalena</t>
-  </si>
-  <si>
-    <t>4B</t>
-  </si>
-  <si>
-    <t>Matematyka</t>
-  </si>
-  <si>
-    <t>30.01.2026, 10, 15:45-16:30, sala: 5</t>
-  </si>
-  <si>
-    <t>30.01.2026, 1, 08:00-08:45, sala: 5</t>
-  </si>
-  <si>
-    <t>Danielewski Paweł</t>
-  </si>
-  <si>
-    <t>2TFB</t>
-  </si>
-  <si>
-    <t>Techniki fryzjerskie</t>
-  </si>
-  <si>
-    <t>30.01.2026, 7, 13:15-14:00, sala: 32</t>
-  </si>
-  <si>
-    <t>30.01.2026, 3, 09:40-10:25, sala: 32</t>
-  </si>
-  <si>
-    <t>Biezmienow Małgorzata</t>
-  </si>
-  <si>
-    <t>5TF</t>
-  </si>
-  <si>
-    <t>Język angielski</t>
-  </si>
-  <si>
-    <t>30.01.2026, 8, 14:05-14:50, sala: 32</t>
-  </si>
-  <si>
-    <t>30.01.2026, 4, 10:35-11:20, sala: 29</t>
-  </si>
-  <si>
-    <t>30.01.2026, 7, 13:15-14:00, sala: 3</t>
-  </si>
-  <si>
-    <t>30.01.2026, 5, 11:25-12:10, sala: 3</t>
-  </si>
-  <si>
-    <t>2TFA</t>
-  </si>
-  <si>
-    <t>30.01.2026, 9, 14:55-15:40, sala: 5</t>
-  </si>
-  <si>
-    <t>30.01.2026, 8, 14:05-14:50, sala: 4</t>
+    <t>01.04.2026, 2, 08:50-09:35, sala: 26</t>
+  </si>
+  <si>
+    <t>01.04.2026, 3, 09:40-10:25, sala: 26</t>
+  </si>
+  <si>
+    <t>Hudziec Agnieszka</t>
+  </si>
+  <si>
+    <t>2FB</t>
+  </si>
+  <si>
+    <t>Chemia</t>
+  </si>
+  <si>
+    <t>30.03.2026, 10, 15:45-16:30, sala: 30</t>
+  </si>
+  <si>
+    <t>01.04.2026, 6, 12:25-13:10, sala: 30</t>
+  </si>
+  <si>
+    <t>Filipek Anna</t>
+  </si>
+  <si>
+    <t>Język polski</t>
   </si>
 </sst>
 </file>
@@ -614,7 +602,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{138a8bf6-f0d9-432d-892c-46e64832422a}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{67afc25b-b530-4215-883e-0456bdb3f553}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -635,16 +623,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{a4f9b3a4-ba69-444d-bd1f-12548d63b4f1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ac9f0d3a-3242-4049-aa22-a6220bfba675}">
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="31.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="22.4285714285714" customWidth="1"/>
+    <col min="1" max="1" width="31.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="31.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="21.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="55.8571428571429" customWidth="1"/>
-    <col min="7" max="7" width="28.1428571428571" customWidth="1"/>
+    <col min="6" max="6" width="44.8571428571429" customWidth="1"/>
+    <col min="7" max="7" width="9.28571428571429" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="56.25" customHeight="1">
@@ -713,27 +702,27 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15">
       <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
         <v>25</v>
-      </c>
-      <c r="F4" t="s">
-        <v>26</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -741,22 +730,22 @@
     </row>
     <row r="5" spans="1:7" ht="15">
       <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
@@ -764,22 +753,22 @@
     </row>
     <row r="6" spans="1:7" ht="15">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
@@ -787,22 +776,22 @@
     </row>
     <row r="7" spans="1:7" ht="15">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
@@ -810,22 +799,22 @@
     </row>
     <row r="8" spans="1:7" ht="15">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G8" t="s">
         <v>15</v>
@@ -833,22 +822,22 @@
     </row>
     <row r="9" spans="1:7" ht="15">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
@@ -856,13 +845,13 @@
     </row>
     <row r="10" spans="1:7" ht="15">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -871,7 +860,7 @@
         <v>35</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>

--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
   <si>
-    <t>Okres: 30.03.2026 (pon.) - 05.04.2026 (niedz.)</t>
+    <t>Okres: 06.04.2026 (pon.) - 12.04.2026 (niedz.)</t>
   </si>
   <si>
     <t>Przeniesiono z</t>
@@ -47,112 +47,43 @@
     <t>Uwagi</t>
   </si>
   <si>
-    <t>30.03.2026, 10, 15:45-16:30, sala: 22</t>
-  </si>
-  <si>
-    <t>30.03.2026, 8, 14:05-14:50, sala: 27</t>
-  </si>
-  <si>
-    <t>Mocarski Arkadiusz</t>
+    <t>08.04.2026, 1, 08:00-08:45, sala: 41</t>
+  </si>
+  <si>
+    <t>08.04.2026, 2, 08:50-09:35, sala: 41</t>
+  </si>
+  <si>
+    <t>Socha Dariusz</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>1CA</t>
-  </si>
-  <si>
-    <t>Technologie produkcji cukierniczej</t>
+    <t>4TH</t>
+  </si>
+  <si>
+    <t>Marketing w działalności handlowej</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>31.03.2026, 7, 13:15-14:00, sala: 34</t>
-  </si>
-  <si>
-    <t>31.03.2026, 2, 08:50-09:35, sala: 31</t>
-  </si>
-  <si>
-    <t>Nowak Magdalena</t>
-  </si>
-  <si>
-    <t>5TF</t>
-  </si>
-  <si>
-    <t>Matematyka</t>
-  </si>
-  <si>
-    <t>31.03.2026, 2, 08:50-09:35, sala: 28</t>
-  </si>
-  <si>
-    <t>31.03.2026, 2, 08:50-09:35, sala: prs</t>
-  </si>
-  <si>
-    <t>Świerzewicz Katarzyna</t>
-  </si>
-  <si>
-    <t>3K</t>
-  </si>
-  <si>
-    <t>Technika w produkcji gastronomicznej</t>
-  </si>
-  <si>
-    <t>31.03.2026, 3, 09:40-10:25, sala: 29</t>
-  </si>
-  <si>
-    <t>31.03.2026, 3, 09:40-10:25, sala: prs</t>
-  </si>
-  <si>
-    <t>Technologia gastronomiczna z towaroznawstwem</t>
-  </si>
-  <si>
-    <t>31.03.2026, 4, 10:35-11:20, sala: 29</t>
-  </si>
-  <si>
-    <t>31.03.2026, 4, 10:35-11:20, sala: prs</t>
-  </si>
-  <si>
-    <t>31.03.2026, 5, 11:25-12:10, sala: 29</t>
-  </si>
-  <si>
-    <t>31.03.2026, 5, 11:25-12:10, sala: prs</t>
-  </si>
-  <si>
-    <t>Zajęcia z wychowawcą</t>
-  </si>
-  <si>
-    <t>31.03.2026, 11, 16:35-17:20, sala: 34</t>
+    <t>08.04.2026, 7, 13:15-14:00, sala: 30</t>
+  </si>
+  <si>
+    <t>08.04.2026, 6, 12:25-13:10, sala: 30</t>
+  </si>
+  <si>
+    <t>Filipek Anna</t>
   </si>
   <si>
     <t>2CB</t>
   </si>
   <si>
-    <t>01.04.2026, 2, 08:50-09:35, sala: 26</t>
-  </si>
-  <si>
-    <t>01.04.2026, 3, 09:40-10:25, sala: 26</t>
-  </si>
-  <si>
-    <t>Hudziec Agnieszka</t>
-  </si>
-  <si>
-    <t>2FB</t>
-  </si>
-  <si>
-    <t>Chemia</t>
-  </si>
-  <si>
-    <t>30.03.2026, 10, 15:45-16:30, sala: 30</t>
-  </si>
-  <si>
-    <t>01.04.2026, 6, 12:25-13:10, sala: 30</t>
-  </si>
-  <si>
-    <t>Filipek Anna</t>
-  </si>
-  <si>
     <t>Język polski</t>
+  </si>
+  <si>
+    <t>p. Filipek, j. polski za lekcję 7</t>
   </si>
 </sst>
 </file>
@@ -602,7 +533,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{67afc25b-b530-4215-883e-0456bdb3f553}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d38d53e2-560f-412d-a2c8-000496cb837d}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -623,17 +554,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ac9f0d3a-3242-4049-aa22-a6220bfba675}">
-  <dimension ref="A1:G10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{85cc4391-da5d-4117-acd1-c7cb3df1a9e8}">
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="31.4285714285714" customWidth="1"/>
-    <col min="3" max="3" width="21.1428571428571" customWidth="1"/>
+    <col min="1" max="2" width="30.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="19.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="44.8571428571429" customWidth="1"/>
-    <col min="7" max="7" width="9.28571428571429" customWidth="1"/>
+    <col min="6" max="6" width="32.8571428571429" customWidth="1"/>
+    <col min="7" max="7" width="26.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="56.25" customHeight="1">
@@ -702,168 +632,7 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15">
-      <c r="A4" t="s">
         <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15">
-      <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15">
-      <c r="A7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15">
-      <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15">
-      <c r="A9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15">
-      <c r="A10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -84,6 +84,60 @@
   </si>
   <si>
     <t>p. Filipek, j. polski za lekcję 7</t>
+  </si>
+  <si>
+    <t>10.04.2026, 8, 14:05-14:50, sala: 18</t>
+  </si>
+  <si>
+    <t>09.04.2026, 9, 14:55-15:40, sala: 18</t>
+  </si>
+  <si>
+    <t>Piątek-Pawłowska Bożena</t>
+  </si>
+  <si>
+    <t>1FA</t>
+  </si>
+  <si>
+    <t>przeniesienie na czwartek, 9.04.2026 lekcja 9</t>
+  </si>
+  <si>
+    <t>09.04.2026, 3, 09:40-10:25, sala: prF3</t>
+  </si>
+  <si>
+    <t>09.04.2026, 10, 15:45-16:30, sala: 23</t>
+  </si>
+  <si>
+    <t>Smirnow-Zechman Eleonora</t>
+  </si>
+  <si>
+    <t>Biznes i zarządzanie</t>
+  </si>
+  <si>
+    <t>10.04.2026, 11, 16:35-17:20, sala: 29</t>
+  </si>
+  <si>
+    <t>09.04.2026, 11, 16:35-17:20, sala: 29</t>
+  </si>
+  <si>
+    <t>Ostrowska Ewa</t>
+  </si>
+  <si>
+    <t>Matematyka</t>
+  </si>
+  <si>
+    <t>matematyka, przeniesiona z 10 kwietnia</t>
+  </si>
+  <si>
+    <t>10.04.2026, 6, 12:25-13:10, sala: 29</t>
+  </si>
+  <si>
+    <t>10.04.2026, 5, 11:25-12:10, sala: 29</t>
+  </si>
+  <si>
+    <t>Bujanowska Iwona</t>
+  </si>
+  <si>
+    <t>1WB</t>
   </si>
 </sst>
 </file>
@@ -533,7 +587,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d38d53e2-560f-412d-a2c8-000496cb837d}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{5cee2ae5-99cb-45cd-896b-66c476641cc0}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -554,16 +608,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{85cc4391-da5d-4117-acd1-c7cb3df1a9e8}">
-  <dimension ref="A1:G3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{def3ac5d-aa1e-4018-a18a-b667143dbb58}">
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="30.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="19.4285714285714" customWidth="1"/>
+    <col min="1" max="1" width="32.5714285714286" customWidth="1"/>
+    <col min="2" max="2" width="31.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
     <col min="6" max="6" width="32.8571428571429" customWidth="1"/>
-    <col min="7" max="7" width="26.5714285714286" customWidth="1"/>
+    <col min="7" max="7" width="40.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="56.25" customHeight="1">
@@ -633,6 +688,98 @@
       </c>
       <c r="G3" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="56">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
   <si>
-    <t>Okres: 06.04.2026 (pon.) - 12.04.2026 (niedz.)</t>
+    <t>Okres: 13.04.2026 (pon.) - 17.04.2026 (pt.)</t>
   </si>
   <si>
     <t>Przeniesiono z</t>
@@ -47,97 +47,145 @@
     <t>Uwagi</t>
   </si>
   <si>
-    <t>08.04.2026, 1, 08:00-08:45, sala: 41</t>
-  </si>
-  <si>
-    <t>08.04.2026, 2, 08:50-09:35, sala: 41</t>
-  </si>
-  <si>
-    <t>Socha Dariusz</t>
+    <t>13.04.2026, 10, 15:45-16:30, sala: 4</t>
+  </si>
+  <si>
+    <t>13.04.2026, 2, 08:50-09:35, sala: 4</t>
+  </si>
+  <si>
+    <t>Kopij Marcin</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4TH</t>
-  </si>
-  <si>
-    <t>Marketing w działalności handlowej</t>
+    <t>2TFA</t>
+  </si>
+  <si>
+    <t>Edukacja obywatelska</t>
+  </si>
+  <si>
+    <t>przeniesienie na lekcję 2</t>
+  </si>
+  <si>
+    <t>13.04.2026, 8, 14:05-14:50, sala: 23</t>
+  </si>
+  <si>
+    <t>13.04.2026, 3, 09:40-10:25, sala: 19</t>
+  </si>
+  <si>
+    <t>Nowak Damiana</t>
+  </si>
+  <si>
+    <t>3TFA</t>
+  </si>
+  <si>
+    <t>Historia</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>08.04.2026, 7, 13:15-14:00, sala: 30</t>
-  </si>
-  <si>
-    <t>08.04.2026, 6, 12:25-13:10, sala: 30</t>
-  </si>
-  <si>
-    <t>Filipek Anna</t>
-  </si>
-  <si>
-    <t>2CB</t>
+    <t>13.04.2026, 3, 09:40-10:25, sala: 33</t>
+  </si>
+  <si>
+    <t>13.04.2026, 6, 12:25-13:10, sala: 33</t>
+  </si>
+  <si>
+    <t>Derezińska Katarzyna</t>
+  </si>
+  <si>
+    <t>2WB</t>
   </si>
   <si>
     <t>Język polski</t>
   </si>
   <si>
-    <t>p. Filipek, j. polski za lekcję 7</t>
-  </si>
-  <si>
-    <t>10.04.2026, 8, 14:05-14:50, sala: 18</t>
-  </si>
-  <si>
-    <t>09.04.2026, 9, 14:55-15:40, sala: 18</t>
-  </si>
-  <si>
-    <t>Piątek-Pawłowska Bożena</t>
-  </si>
-  <si>
-    <t>1FA</t>
-  </si>
-  <si>
-    <t>przeniesienie na czwartek, 9.04.2026 lekcja 9</t>
-  </si>
-  <si>
-    <t>09.04.2026, 3, 09:40-10:25, sala: prF3</t>
-  </si>
-  <si>
-    <t>09.04.2026, 10, 15:45-16:30, sala: 23</t>
-  </si>
-  <si>
-    <t>Smirnow-Zechman Eleonora</t>
-  </si>
-  <si>
-    <t>Biznes i zarządzanie</t>
-  </si>
-  <si>
-    <t>10.04.2026, 11, 16:35-17:20, sala: 29</t>
-  </si>
-  <si>
-    <t>09.04.2026, 11, 16:35-17:20, sala: 29</t>
+    <t>15.04.2026, 9, 14:55-15:40, sala: 4</t>
+  </si>
+  <si>
+    <t>15.04.2026, 6, 12:25-13:10, sala: 4</t>
+  </si>
+  <si>
+    <t>2K</t>
+  </si>
+  <si>
+    <t>15.04.2026, 9, 14:55-15:40, sala: 29</t>
+  </si>
+  <si>
+    <t>15.04.2026, 9, 14:55-15:40, sala: 3</t>
   </si>
   <si>
     <t>Ostrowska Ewa</t>
   </si>
   <si>
+    <t>1CB</t>
+  </si>
+  <si>
     <t>Matematyka</t>
   </si>
   <si>
-    <t>matematyka, przeniesiona z 10 kwietnia</t>
-  </si>
-  <si>
-    <t>10.04.2026, 6, 12:25-13:10, sala: 29</t>
-  </si>
-  <si>
-    <t>10.04.2026, 5, 11:25-12:10, sala: 29</t>
-  </si>
-  <si>
-    <t>Bujanowska Iwona</t>
-  </si>
-  <si>
-    <t>1WB</t>
+    <t>15.04.2026, 3, 09:40-10:25, sala: 04</t>
+  </si>
+  <si>
+    <t>15.04.2026, 10, 15:45-16:30, sala: 4</t>
+  </si>
+  <si>
+    <t>Wojciechowski Łukasz</t>
+  </si>
+  <si>
+    <t>2FA|JA1</t>
+  </si>
+  <si>
+    <t>Język angielski</t>
+  </si>
+  <si>
+    <t>j. angielski przeniesiony na 10 lekcję</t>
+  </si>
+  <si>
+    <t>16.04.2026, 1, 08:00-08:45, sala: 4</t>
+  </si>
+  <si>
+    <t>16.04.2026, 2, 08:50-09:35, sala: 4</t>
+  </si>
+  <si>
+    <t>5TF</t>
+  </si>
+  <si>
+    <t>Wiedza o społeczeństwie</t>
+  </si>
+  <si>
+    <t>16.04.2026, 11, 16:35-17:20, sala: 31</t>
+  </si>
+  <si>
+    <t>16.04.2026, 8, 14:05-14:50, sala: 31</t>
+  </si>
+  <si>
+    <t>Smereka Alicja</t>
+  </si>
+  <si>
+    <t>2TFB</t>
+  </si>
+  <si>
+    <t>Geografia</t>
+  </si>
+  <si>
+    <t>13.04.2026, 3, 09:40-10:25, sala: 17</t>
+  </si>
+  <si>
+    <t>17.04.2026, 4, 10:35-11:20, sala: 3</t>
+  </si>
+  <si>
+    <t>Filusz Marzena</t>
+  </si>
+  <si>
+    <t>13.04.2026, 2, 08:50-09:35, sala: 17</t>
+  </si>
+  <si>
+    <t>17.04.2026, 7, 13:15-14:00, sala: 3</t>
+  </si>
+  <si>
+    <t>3TFB</t>
   </si>
 </sst>
 </file>
@@ -587,7 +635,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{5cee2ae5-99cb-45cd-896b-66c476641cc0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{51fb71b2-5455-4184-bfdf-395876928bac}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -608,17 +656,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{def3ac5d-aa1e-4018-a18a-b667143dbb58}">
-  <dimension ref="A1:G7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{bfdfd4cc-89c1-40d5-a8da-c153fd602bfe}">
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32.5714285714286" customWidth="1"/>
-    <col min="2" max="2" width="31.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
+    <col min="1" max="1" width="31.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="30.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="20.7142857142857" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="32.8571428571429" customWidth="1"/>
-    <col min="7" max="7" width="40.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="23.5714285714286" customWidth="1"/>
+    <col min="7" max="7" width="33.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="56.25" customHeight="1">
@@ -707,10 +755,10 @@
         <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15">
@@ -721,65 +769,157 @@
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15">
       <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
         <v>31</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>32</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
         <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15">
       <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
         <v>36</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>37</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" t="s">
         <v>39</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
         <v>34</v>
       </c>
-      <c r="G7" t="s">
-        <v>15</v>
+      <c r="G10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15">
+      <c r="A11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -23,7 +23,7 @@
     <t>Rok szkolny: 2025/2026</t>
   </si>
   <si>
-    <t>Okres: 13.04.2026 (pon.) - 17.04.2026 (pt.)</t>
+    <t>Okres: 13.04.2026 (pon.) - 19.04.2026 (niedz.)</t>
   </si>
   <si>
     <t>Przeniesiono z</t>
@@ -635,7 +635,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{51fb71b2-5455-4184-bfdf-395876928bac}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{01ccacfa-8d67-4352-afbb-904790c4effe}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -656,7 +656,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{bfdfd4cc-89c1-40d5-a8da-c153fd602bfe}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{70a9875e-905e-4d50-b0db-db4b08caf8fe}">
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>

--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="58">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -89,7 +89,7 @@
     <t>13.04.2026, 3, 09:40-10:25, sala: 33</t>
   </si>
   <si>
-    <t>13.04.2026, 6, 12:25-13:10, sala: 33</t>
+    <t>13.04.2026, 6, 12:25-13:10, sala: 32</t>
   </si>
   <si>
     <t>Derezińska Katarzyna</t>
@@ -110,6 +110,42 @@
     <t>2K</t>
   </si>
   <si>
+    <t>15.04.2026, 1, 08:00-08:45, sala: 44</t>
+  </si>
+  <si>
+    <t>15.04.2026, 6, 12:25-13:10, sala: 43</t>
+  </si>
+  <si>
+    <t>Misiąg Anna</t>
+  </si>
+  <si>
+    <t>1TH|JA1</t>
+  </si>
+  <si>
+    <t>Język niemiecki</t>
+  </si>
+  <si>
+    <t>p. Misiąg, j. niemiecki za lekcję 1</t>
+  </si>
+  <si>
+    <t>13.04.2026, 2, 08:50-09:35, sala: 17</t>
+  </si>
+  <si>
+    <t>15.04.2026, 8, 14:05-14:50, sala: 23</t>
+  </si>
+  <si>
+    <t>Filusz Marzena</t>
+  </si>
+  <si>
+    <t>3TFB</t>
+  </si>
+  <si>
+    <t>Matematyka</t>
+  </si>
+  <si>
+    <t>matematyka, przeniesiona na środę 15.04.2026 8 lekcja, sala 23</t>
+  </si>
+  <si>
     <t>15.04.2026, 9, 14:55-15:40, sala: 29</t>
   </si>
   <si>
@@ -122,9 +158,6 @@
     <t>1CB</t>
   </si>
   <si>
-    <t>Matematyka</t>
-  </si>
-  <si>
     <t>15.04.2026, 3, 09:40-10:25, sala: 04</t>
   </si>
   <si>
@@ -155,37 +188,10 @@
     <t>Wiedza o społeczeństwie</t>
   </si>
   <si>
-    <t>16.04.2026, 11, 16:35-17:20, sala: 31</t>
-  </si>
-  <si>
-    <t>16.04.2026, 8, 14:05-14:50, sala: 31</t>
-  </si>
-  <si>
-    <t>Smereka Alicja</t>
-  </si>
-  <si>
-    <t>2TFB</t>
-  </si>
-  <si>
-    <t>Geografia</t>
-  </si>
-  <si>
     <t>13.04.2026, 3, 09:40-10:25, sala: 17</t>
   </si>
   <si>
     <t>17.04.2026, 4, 10:35-11:20, sala: 3</t>
-  </si>
-  <si>
-    <t>Filusz Marzena</t>
-  </si>
-  <si>
-    <t>13.04.2026, 2, 08:50-09:35, sala: 17</t>
-  </si>
-  <si>
-    <t>17.04.2026, 7, 13:15-14:00, sala: 3</t>
-  </si>
-  <si>
-    <t>3TFB</t>
   </si>
 </sst>
 </file>
@@ -635,7 +641,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{01ccacfa-8d67-4352-afbb-904790c4effe}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{bc2dfba6-690a-4a7e-b068-0eda0c3e2295}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -656,17 +662,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{70a9875e-905e-4d50-b0db-db4b08caf8fe}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d9b2312c-15ec-49ea-83dd-3390c05e6062}">
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="30.7142857142857" customWidth="1"/>
+    <col min="1" max="2" width="30.7142857142857" customWidth="1"/>
     <col min="3" max="3" width="20.7142857142857" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
     <col min="6" max="6" width="23.5714285714286" customWidth="1"/>
-    <col min="7" max="7" width="33.1428571428571" customWidth="1"/>
+    <col min="7" max="7" width="56" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="56.25" customHeight="1">
@@ -804,50 +809,50 @@
         <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s">
         <v>21</v>
@@ -855,45 +860,45 @@
     </row>
     <row r="9" spans="1:7" ht="15">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="G10" t="s">
         <v>21</v>
@@ -901,22 +906,22 @@
     </row>
     <row r="11" spans="1:7" ht="15">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G11" t="s">
         <v>21</v>

--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="63">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -99,6 +99,21 @@
   </si>
   <si>
     <t>Język polski</t>
+  </si>
+  <si>
+    <t>14.04.2026, 9, 14:55-15:40, sala: 40</t>
+  </si>
+  <si>
+    <t>14.04.2026, 9, 14:55-15:40, sala: 42</t>
+  </si>
+  <si>
+    <t>Płatek Krzysztof</t>
+  </si>
+  <si>
+    <t>1K|JA1</t>
+  </si>
+  <si>
+    <t>Edukacja dla bezpieczeństwa</t>
   </si>
   <si>
     <t>15.04.2026, 9, 14:55-15:40, sala: 4</t>
@@ -641,7 +656,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{bc2dfba6-690a-4a7e-b068-0eda0c3e2295}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f5485f29-fb95-4fc0-b046-006ee34f6f9b}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -662,15 +677,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d9b2312c-15ec-49ea-83dd-3390c05e6062}">
-  <dimension ref="A1:G11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{77131b54-bbfe-4e36-b11d-5aadaf741b90}">
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="30.7142857142857" customWidth="1"/>
     <col min="3" max="3" width="20.7142857142857" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="23.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="26.7142857142857" customWidth="1"/>
     <col min="7" max="7" width="56" customWidth="1"/>
   </cols>
   <sheetData>
@@ -774,16 +789,16 @@
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G5" t="s">
         <v>21</v>
@@ -791,105 +806,105 @@
     </row>
     <row r="6" spans="1:7" ht="15">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15">
       <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
         <v>36</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
         <v>38</v>
       </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>39</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>40</v>
-      </c>
-      <c r="G7" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15">
       <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
         <v>42</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>43</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
         <v>44</v>
       </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>45</v>
       </c>
-      <c r="F8" t="s">
-        <v>40</v>
-      </c>
       <c r="G8" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G9" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15">
       <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
         <v>52</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>53</v>
-      </c>
-      <c r="C10" t="s">
-        <v>11</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -901,29 +916,52 @@
         <v>55</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
         <v>19</v>
       </c>
-      <c r="F11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="F12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" t="s">
         <v>21</v>
       </c>
     </row>

--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
   <si>
-    <t>Okres: 13.04.2026 (pon.) - 19.04.2026 (niedz.)</t>
+    <t>Okres: 20.04.2026 (pon.) - 24.04.2026 (pt.)</t>
   </si>
   <si>
     <t>Przeniesiono z</t>
@@ -47,166 +47,49 @@
     <t>Uwagi</t>
   </si>
   <si>
-    <t>13.04.2026, 10, 15:45-16:30, sala: 4</t>
-  </si>
-  <si>
-    <t>13.04.2026, 2, 08:50-09:35, sala: 4</t>
-  </si>
-  <si>
-    <t>Kopij Marcin</t>
+    <t>20.04.2026, 10, 15:45-16:30, sala: 33</t>
+  </si>
+  <si>
+    <t>20.04.2026, 7, 13:15-14:00, sala: 33</t>
+  </si>
+  <si>
+    <t>Derezińska Katarzyna</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>2TFA</t>
-  </si>
-  <si>
-    <t>Edukacja obywatelska</t>
-  </si>
-  <si>
-    <t>przeniesienie na lekcję 2</t>
-  </si>
-  <si>
-    <t>13.04.2026, 8, 14:05-14:50, sala: 23</t>
-  </si>
-  <si>
-    <t>13.04.2026, 3, 09:40-10:25, sala: 19</t>
-  </si>
-  <si>
-    <t>Nowak Damiana</t>
-  </si>
-  <si>
-    <t>3TFA</t>
-  </si>
-  <si>
-    <t>Historia</t>
+    <t>2K</t>
+  </si>
+  <si>
+    <t>Zajęcia z wychowawcą</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>13.04.2026, 3, 09:40-10:25, sala: 33</t>
-  </si>
-  <si>
-    <t>13.04.2026, 6, 12:25-13:10, sala: 32</t>
-  </si>
-  <si>
-    <t>Derezińska Katarzyna</t>
-  </si>
-  <si>
-    <t>2WB</t>
-  </si>
-  <si>
-    <t>Język polski</t>
-  </si>
-  <si>
-    <t>14.04.2026, 9, 14:55-15:40, sala: 40</t>
-  </si>
-  <si>
-    <t>14.04.2026, 9, 14:55-15:40, sala: 42</t>
-  </si>
-  <si>
-    <t>Płatek Krzysztof</t>
-  </si>
-  <si>
-    <t>1K|JA1</t>
-  </si>
-  <si>
-    <t>Edukacja dla bezpieczeństwa</t>
-  </si>
-  <si>
-    <t>15.04.2026, 9, 14:55-15:40, sala: 4</t>
-  </si>
-  <si>
-    <t>15.04.2026, 6, 12:25-13:10, sala: 4</t>
-  </si>
-  <si>
-    <t>2K</t>
-  </si>
-  <si>
-    <t>15.04.2026, 1, 08:00-08:45, sala: 44</t>
-  </si>
-  <si>
-    <t>15.04.2026, 6, 12:25-13:10, sala: 43</t>
-  </si>
-  <si>
-    <t>Misiąg Anna</t>
-  </si>
-  <si>
-    <t>1TH|JA1</t>
-  </si>
-  <si>
-    <t>Język niemiecki</t>
-  </si>
-  <si>
-    <t>p. Misiąg, j. niemiecki za lekcję 1</t>
-  </si>
-  <si>
-    <t>13.04.2026, 2, 08:50-09:35, sala: 17</t>
-  </si>
-  <si>
-    <t>15.04.2026, 8, 14:05-14:50, sala: 23</t>
-  </si>
-  <si>
-    <t>Filusz Marzena</t>
-  </si>
-  <si>
-    <t>3TFB</t>
+    <t>22.04.2026, 9, 14:55-15:40, sala: 29</t>
+  </si>
+  <si>
+    <t>22.04.2026, 9, 14:55-15:40, sala: 3</t>
+  </si>
+  <si>
+    <t>Ostrowska Ewa</t>
+  </si>
+  <si>
+    <t>1CB</t>
   </si>
   <si>
     <t>Matematyka</t>
   </si>
   <si>
-    <t>matematyka, przeniesiona na środę 15.04.2026 8 lekcja, sala 23</t>
-  </si>
-  <si>
-    <t>15.04.2026, 9, 14:55-15:40, sala: 29</t>
-  </si>
-  <si>
-    <t>15.04.2026, 9, 14:55-15:40, sala: 3</t>
-  </si>
-  <si>
-    <t>Ostrowska Ewa</t>
-  </si>
-  <si>
-    <t>1CB</t>
-  </si>
-  <si>
-    <t>15.04.2026, 3, 09:40-10:25, sala: 04</t>
-  </si>
-  <si>
-    <t>15.04.2026, 10, 15:45-16:30, sala: 4</t>
-  </si>
-  <si>
-    <t>Wojciechowski Łukasz</t>
-  </si>
-  <si>
-    <t>2FA|JA1</t>
-  </si>
-  <si>
-    <t>Język angielski</t>
-  </si>
-  <si>
-    <t>j. angielski przeniesiony na 10 lekcję</t>
-  </si>
-  <si>
-    <t>16.04.2026, 1, 08:00-08:45, sala: 4</t>
-  </si>
-  <si>
-    <t>16.04.2026, 2, 08:50-09:35, sala: 4</t>
-  </si>
-  <si>
-    <t>5TF</t>
-  </si>
-  <si>
-    <t>Wiedza o społeczeństwie</t>
-  </si>
-  <si>
-    <t>13.04.2026, 3, 09:40-10:25, sala: 17</t>
-  </si>
-  <si>
-    <t>17.04.2026, 4, 10:35-11:20, sala: 3</t>
+    <t>24.04.2026, 11, 16:35-17:20, sala: 29</t>
+  </si>
+  <si>
+    <t>24.04.2026, 11, 16:35-17:20, sala: 28</t>
+  </si>
+  <si>
+    <t>1FA</t>
   </si>
 </sst>
 </file>
@@ -656,7 +539,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f5485f29-fb95-4fc0-b046-006ee34f6f9b}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{078c19a7-773b-4c63-8cfe-f9f8c5f4fa45}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -677,16 +560,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{77131b54-bbfe-4e36-b11d-5aadaf741b90}">
-  <dimension ref="A1:G12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{9ba3648a-b108-4cf2-b932-d555284ca5dc}">
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="30.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="20.7142857142857" customWidth="1"/>
+    <col min="1" max="2" width="31.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="26.7142857142857" customWidth="1"/>
-    <col min="7" max="7" width="56" customWidth="1"/>
+    <col min="6" max="6" width="20.7142857142857" customWidth="1"/>
+    <col min="7" max="7" width="9.28571428571429" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="56.25" customHeight="1">
@@ -755,214 +638,30 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15">
       <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15">
-      <c r="A6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15">
-      <c r="A8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15">
-      <c r="A9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15">
-      <c r="A10" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15">
-      <c r="A11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
-        <v>59</v>
-      </c>
-      <c r="F11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15">
-      <c r="A12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
   <si>
-    <t>Okres: 20.04.2026 (pon.) - 24.04.2026 (pt.)</t>
+    <t>Okres: 20.04.2026 (pon.) - 26.04.2026 (niedz.)</t>
   </si>
   <si>
     <t>Przeniesiono z</t>
@@ -66,6 +66,21 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>21.04.2026, 1, 08:00-08:45, sala: 22</t>
+  </si>
+  <si>
+    <t>22.04.2026, 7, 13:15-14:00, sala: 42</t>
+  </si>
+  <si>
+    <t>Ulanowska Magdalena</t>
+  </si>
+  <si>
+    <t>2TH</t>
+  </si>
+  <si>
+    <t>p. Ulanowska, zajęcia z wychowawcą przeniesione na środę 22.04 7 lekcja, sala 42</t>
   </si>
   <si>
     <t>22.04.2026, 9, 14:55-15:40, sala: 29</t>
@@ -539,7 +554,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{078c19a7-773b-4c63-8cfe-f9f8c5f4fa45}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{54eaee9a-c405-4f70-9991-87161a9557a4}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -560,16 +575,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{9ba3648a-b108-4cf2-b932-d555284ca5dc}">
-  <dimension ref="A1:G4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{40a4179d-3232-4e9f-a25b-02e72aec084f}">
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="31.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
     <col min="6" max="6" width="20.7142857142857" customWidth="1"/>
-    <col min="7" max="7" width="9.28571428571429" customWidth="1"/>
+    <col min="7" max="7" width="72" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="56.25" customHeight="1">
@@ -635,10 +650,10 @@
         <v>19</v>
       </c>
       <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
         <v>20</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15">
@@ -649,18 +664,41 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
         <v>23</v>
       </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
         <v>15</v>
       </c>
     </row>

--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="46">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -68,6 +68,39 @@
     <t/>
   </si>
   <si>
+    <t>22.04.2026, 1, 08:00-08:45, sala: 41</t>
+  </si>
+  <si>
+    <t>22.04.2026, 2, 08:50-09:35, sala: 41</t>
+  </si>
+  <si>
+    <t>Socha Dariusz</t>
+  </si>
+  <si>
+    <t>4TH</t>
+  </si>
+  <si>
+    <t>Marketing w działalności handlowej</t>
+  </si>
+  <si>
+    <t>22.04.2026, 1, 08:00-08:45, sala: 44</t>
+  </si>
+  <si>
+    <t>22.04.2026, 6, 12:25-13:10, sala: 41</t>
+  </si>
+  <si>
+    <t>Misiąg Anna</t>
+  </si>
+  <si>
+    <t>1TH|JA1</t>
+  </si>
+  <si>
+    <t>Język niemiecki</t>
+  </si>
+  <si>
+    <t>j. niemiecki, przeniesiony na lekcję 6, sala 41</t>
+  </si>
+  <si>
     <t>21.04.2026, 1, 08:00-08:45, sala: 22</t>
   </si>
   <si>
@@ -96,6 +129,24 @@
   </si>
   <si>
     <t>Matematyka</t>
+  </si>
+  <si>
+    <t>23.04.2026, 8, 14:05-14:50, sala: 32</t>
+  </si>
+  <si>
+    <t>23.04.2026, 1, 08:00-08:45, sala: 32</t>
+  </si>
+  <si>
+    <t>Biezmienow Małgorzata</t>
+  </si>
+  <si>
+    <t>1TFB|JA1</t>
+  </si>
+  <si>
+    <t>Język angielski</t>
+  </si>
+  <si>
+    <t>j. angielski przeniesiony na 1 lekcję, sala 32</t>
   </si>
   <si>
     <t>24.04.2026, 11, 16:35-17:20, sala: 29</t>
@@ -554,7 +605,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{54eaee9a-c405-4f70-9991-87161a9557a4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4119ea6c-f0b6-4450-99bd-9cd5c38326b1}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -575,15 +626,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{40a4179d-3232-4e9f-a25b-02e72aec084f}">
-  <dimension ref="A1:G5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ebe29129-ac6b-4166-980e-dadec9913b06}">
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="31.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="3" max="3" width="22.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="20.7142857142857" customWidth="1"/>
+    <col min="6" max="6" width="32.8571428571429" customWidth="1"/>
     <col min="7" max="7" width="72" customWidth="1"/>
   </cols>
   <sheetData>
@@ -650,10 +701,10 @@
         <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15">
@@ -676,29 +727,98 @@
         <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" t="s">
         <v>15</v>
       </c>
     </row>

--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -605,7 +605,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4119ea6c-f0b6-4450-99bd-9cd5c38326b1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{1939433e-90ef-4552-8599-ec6bacc862f0}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -626,7 +626,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ebe29129-ac6b-4166-980e-dadec9913b06}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{91412894-ede2-4739-bee7-6c2f381db466}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>

--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="52">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -116,46 +116,64 @@
     <t>p. Ulanowska, zajęcia z wychowawcą przeniesione na środę 22.04 7 lekcja, sala 42</t>
   </si>
   <si>
-    <t>22.04.2026, 9, 14:55-15:40, sala: 29</t>
-  </si>
-  <si>
-    <t>22.04.2026, 9, 14:55-15:40, sala: 3</t>
+    <t>23.04.2026, 8, 14:05-14:50, sala: 32</t>
+  </si>
+  <si>
+    <t>23.04.2026, 1, 08:00-08:45, sala: 32</t>
+  </si>
+  <si>
+    <t>Biezmienow Małgorzata</t>
+  </si>
+  <si>
+    <t>1TFB|JA1</t>
+  </si>
+  <si>
+    <t>Język angielski</t>
+  </si>
+  <si>
+    <t>j. angielski przeniesiony na 1 lekcję, sala 32</t>
+  </si>
+  <si>
+    <t>24.04.2026, 9, 14:55-15:40, sala: 2</t>
+  </si>
+  <si>
+    <t>24.04.2026, 2, 08:50-09:35, sala: 2</t>
+  </si>
+  <si>
+    <t>Leńczowska Iwona</t>
+  </si>
+  <si>
+    <t>1FC</t>
+  </si>
+  <si>
+    <t>Techniki fryzjerskie</t>
+  </si>
+  <si>
+    <t>24.04.2026, 9, 14:55-15:40, sala: 4</t>
+  </si>
+  <si>
+    <t>24.04.2026, 3, 09:40-10:25, sala: 4</t>
+  </si>
+  <si>
+    <t>Danielewski Paweł</t>
+  </si>
+  <si>
+    <t>3TFA</t>
+  </si>
+  <si>
+    <t>24.04.2026, 11, 16:35-17:20, sala: 29</t>
+  </si>
+  <si>
+    <t>24.04.2026, 11, 16:35-17:20, sala: 28</t>
   </si>
   <si>
     <t>Ostrowska Ewa</t>
   </si>
   <si>
-    <t>1CB</t>
+    <t>1FA</t>
   </si>
   <si>
     <t>Matematyka</t>
-  </si>
-  <si>
-    <t>23.04.2026, 8, 14:05-14:50, sala: 32</t>
-  </si>
-  <si>
-    <t>23.04.2026, 1, 08:00-08:45, sala: 32</t>
-  </si>
-  <si>
-    <t>Biezmienow Małgorzata</t>
-  </si>
-  <si>
-    <t>1TFB|JA1</t>
-  </si>
-  <si>
-    <t>Język angielski</t>
-  </si>
-  <si>
-    <t>j. angielski przeniesiony na 1 lekcję, sala 32</t>
-  </si>
-  <si>
-    <t>24.04.2026, 11, 16:35-17:20, sala: 29</t>
-  </si>
-  <si>
-    <t>24.04.2026, 11, 16:35-17:20, sala: 28</t>
-  </si>
-  <si>
-    <t>1FA</t>
   </si>
 </sst>
 </file>
@@ -605,7 +623,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{1939433e-90ef-4552-8599-ec6bacc862f0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{2d039c31-82dd-4741-a82d-34cb1916ba14}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -626,8 +644,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{91412894-ede2-4739-bee7-6c2f381db466}">
-  <dimension ref="A1:G8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{6bb92af8-354a-42ab-a96e-afd46281f8ae}">
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="31.7142857142857" customWidth="1"/>
@@ -773,30 +791,30 @@
         <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15">
@@ -807,18 +825,41 @@
         <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" t="s">
         <v>15</v>
       </c>
     </row>

--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="73">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
   <si>
-    <t>Okres: 20.04.2026 (pon.) - 26.04.2026 (niedz.)</t>
+    <t>Okres: 27.04.2026 (pon.) - 01.05.2026 (pt.)</t>
   </si>
   <si>
     <t>Przeniesiono z</t>
@@ -47,10 +47,10 @@
     <t>Uwagi</t>
   </si>
   <si>
-    <t>20.04.2026, 10, 15:45-16:30, sala: 33</t>
-  </si>
-  <si>
-    <t>20.04.2026, 7, 13:15-14:00, sala: 33</t>
+    <t>27.04.2026, 10, 15:45-16:30, sala: 33</t>
+  </si>
+  <si>
+    <t>27.04.2026, 6, 12:25-13:10, sala: 33</t>
   </si>
   <si>
     <t>Derezińska Katarzyna</t>
@@ -68,112 +68,175 @@
     <t/>
   </si>
   <si>
-    <t>22.04.2026, 1, 08:00-08:45, sala: 41</t>
-  </si>
-  <si>
-    <t>22.04.2026, 2, 08:50-09:35, sala: 41</t>
-  </si>
-  <si>
-    <t>Socha Dariusz</t>
-  </si>
-  <si>
-    <t>4TH</t>
-  </si>
-  <si>
-    <t>Marketing w działalności handlowej</t>
-  </si>
-  <si>
-    <t>22.04.2026, 1, 08:00-08:45, sala: 44</t>
-  </si>
-  <si>
-    <t>22.04.2026, 6, 12:25-13:10, sala: 41</t>
-  </si>
-  <si>
-    <t>Misiąg Anna</t>
-  </si>
-  <si>
-    <t>1TH|JA1</t>
-  </si>
-  <si>
-    <t>Język niemiecki</t>
-  </si>
-  <si>
-    <t>j. niemiecki, przeniesiony na lekcję 6, sala 41</t>
-  </si>
-  <si>
-    <t>21.04.2026, 1, 08:00-08:45, sala: 22</t>
-  </si>
-  <si>
-    <t>22.04.2026, 7, 13:15-14:00, sala: 42</t>
-  </si>
-  <si>
-    <t>Ulanowska Magdalena</t>
-  </si>
-  <si>
-    <t>2TH</t>
-  </si>
-  <si>
-    <t>p. Ulanowska, zajęcia z wychowawcą przeniesione na środę 22.04 7 lekcja, sala 42</t>
-  </si>
-  <si>
-    <t>23.04.2026, 8, 14:05-14:50, sala: 32</t>
-  </si>
-  <si>
-    <t>23.04.2026, 1, 08:00-08:45, sala: 32</t>
+    <t>29.04.2026, 9, 14:55-15:40, sala: 40</t>
+  </si>
+  <si>
+    <t>27.04.2026, 6, 12:25-13:10, sala: prs</t>
+  </si>
+  <si>
+    <t>Filiczak Agnieszka</t>
+  </si>
+  <si>
+    <t>2CB</t>
+  </si>
+  <si>
+    <t>Technika w produkcji cukierniczej</t>
+  </si>
+  <si>
+    <t>p. Filiczak, Technika przeniesiona ze środy 29 kwietnia na poniedziałek lekcja 6, pracownia spożywcza</t>
+  </si>
+  <si>
+    <t>27.04.2026, 10, 15:45-16:30, sala: 30</t>
+  </si>
+  <si>
+    <t>27.04.2026, 7, 13:15-14:00, sala: 22</t>
+  </si>
+  <si>
+    <t>Filipek Anna</t>
+  </si>
+  <si>
+    <t>Język polski</t>
+  </si>
+  <si>
+    <t>p. Filipek, j. polski za lekcję 10, sala 22</t>
+  </si>
+  <si>
+    <t>27.04.2026, 1, 08:00-08:45, sala: 32</t>
+  </si>
+  <si>
+    <t>27.04.2026, 9, 14:55-15:40, sala: 32</t>
   </si>
   <si>
     <t>Biezmienow Małgorzata</t>
   </si>
   <si>
-    <t>1TFB|JA1</t>
+    <t>2S</t>
   </si>
   <si>
     <t>Język angielski</t>
   </si>
   <si>
-    <t>j. angielski przeniesiony na 1 lekcję, sala 32</t>
-  </si>
-  <si>
-    <t>24.04.2026, 9, 14:55-15:40, sala: 2</t>
-  </si>
-  <si>
-    <t>24.04.2026, 2, 08:50-09:35, sala: 2</t>
-  </si>
-  <si>
-    <t>Leńczowska Iwona</t>
-  </si>
-  <si>
-    <t>1FC</t>
-  </si>
-  <si>
-    <t>Techniki fryzjerskie</t>
-  </si>
-  <si>
-    <t>24.04.2026, 9, 14:55-15:40, sala: 4</t>
-  </si>
-  <si>
-    <t>24.04.2026, 3, 09:40-10:25, sala: 4</t>
-  </si>
-  <si>
-    <t>Danielewski Paweł</t>
-  </si>
-  <si>
-    <t>3TFA</t>
-  </si>
-  <si>
-    <t>24.04.2026, 11, 16:35-17:20, sala: 29</t>
-  </si>
-  <si>
-    <t>24.04.2026, 11, 16:35-17:20, sala: 28</t>
+    <t>j. angielski przeniesiony na 9 lekcję, sala 32</t>
+  </si>
+  <si>
+    <t>29.04.2026, 8, 14:05-14:50, sala: 43</t>
+  </si>
+  <si>
+    <t>28.04.2026, 2, 08:50-09:35, sala: 43</t>
+  </si>
+  <si>
+    <t>Staliś Donata</t>
+  </si>
+  <si>
+    <t>3TFA|JA2</t>
+  </si>
+  <si>
+    <t>j. angielski, przeniesiony na wtorek, 2 lekcja, sala 43</t>
+  </si>
+  <si>
+    <t>27.04.2026, 6, 12:25-13:10, sala: 30</t>
+  </si>
+  <si>
+    <t>29.04.2026, 5, 11:25-12:10, sala: 34</t>
+  </si>
+  <si>
+    <t>Kończyńska Małgorzata</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - dekoracje w cukiernictwie</t>
+  </si>
+  <si>
+    <t>p. Kończyńska, RKZ przeniesiony na środę 29 kwietnia, lekcja 5, sala 34</t>
+  </si>
+  <si>
+    <t>28.04.2026, 2, 08:50-09:35, sala: 32</t>
+  </si>
+  <si>
+    <t>29.04.2026, 8, 14:05-14:50, sala: 32</t>
+  </si>
+  <si>
+    <t>3TFB|JA1</t>
+  </si>
+  <si>
+    <t>j. angielski przeniesiony na środę, 8 lekcja, sala 32</t>
+  </si>
+  <si>
+    <t>30.04.2026, 8, 14:05-14:50, sala: 4</t>
+  </si>
+  <si>
+    <t>29.04.2026, 8, 14:05-14:50, sala: 4</t>
+  </si>
+  <si>
+    <t>Kruk Marcin</t>
+  </si>
+  <si>
+    <t>1FA</t>
+  </si>
+  <si>
+    <t>Chemia</t>
+  </si>
+  <si>
+    <t>29.04.2026, 9, 14:55-15:40, sala: 4</t>
+  </si>
+  <si>
+    <t>29.04.2026, 9, 14:55-15:40, sala: 2</t>
+  </si>
+  <si>
+    <t>Kopij Marcin</t>
+  </si>
+  <si>
+    <t>Edukacja obywatelska</t>
+  </si>
+  <si>
+    <t>30.04.2026, 9, 14:55-15:40, sala: 4</t>
+  </si>
+  <si>
+    <t>29.04.2026, 9, 14:55-15:40, sala: 5</t>
+  </si>
+  <si>
+    <t>2B</t>
+  </si>
+  <si>
+    <t>Zajęcia praktyczne - projektowanie i wykonywanie fryzur</t>
+  </si>
+  <si>
+    <t>29.04.2026, 9, 14:55-15:40, sala: 29</t>
+  </si>
+  <si>
+    <t>29.04.2026, 9, 14:55-15:40, sala: 3</t>
   </si>
   <si>
     <t>Ostrowska Ewa</t>
   </si>
   <si>
-    <t>1FA</t>
+    <t>1CB</t>
   </si>
   <si>
     <t>Matematyka</t>
+  </si>
+  <si>
+    <t>30.04.2026, 10, 15:45-16:30, sala: 4</t>
+  </si>
+  <si>
+    <t>29.04.2026, 10, 15:45-16:30, sala: 4</t>
+  </si>
+  <si>
+    <t>30.04.2026, 11, 16:35-17:20, sala: 4</t>
+  </si>
+  <si>
+    <t>29.04.2026, 11, 16:35-17:20, sala: 4</t>
+  </si>
+  <si>
+    <t>30.04.2026, 12, 17:25-18:10, sala: 4</t>
+  </si>
+  <si>
+    <t>29.04.2026, 12, 17:25-18:10, sala: 4</t>
+  </si>
+  <si>
+    <t>30.04.2026, 13, 18:15-19:00, sala: 4</t>
+  </si>
+  <si>
+    <t>29.04.2026, 13, 18:15-19:00, sala: 4</t>
   </si>
 </sst>
 </file>
@@ -623,7 +686,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{2d039c31-82dd-4741-a82d-34cb1916ba14}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{43eac707-a56e-472c-b12e-a707f1c402fc}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -644,16 +707,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{6bb92af8-354a-42ab-a96e-afd46281f8ae}">
-  <dimension ref="A1:G9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{54a5feed-29c3-4eb2-864e-f672dee7fc4f}">
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="31.7142857142857" customWidth="1"/>
+    <col min="1" max="1" width="31.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="31.4285714285714" customWidth="1"/>
     <col min="3" max="3" width="22.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="32.8571428571429" customWidth="1"/>
-    <col min="7" max="7" width="72" customWidth="1"/>
+    <col min="6" max="6" width="55.8571428571429" customWidth="1"/>
+    <col min="7" max="7" width="90.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="56.25" customHeight="1">
@@ -722,24 +786,24 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
         <v>25</v>
@@ -765,30 +829,30 @@
         <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G6" t="s">
         <v>37</v>
@@ -808,13 +872,13 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
         <v>41</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>42</v>
-      </c>
-      <c r="G7" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15">
@@ -825,19 +889,19 @@
         <v>44</v>
       </c>
       <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
         <v>45</v>
       </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" t="s">
         <v>46</v>
-      </c>
-      <c r="F8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15">
@@ -860,6 +924,167 @@
         <v>51</v>
       </c>
       <c r="G9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15">
+      <c r="A11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15">
+      <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15">
+      <c r="A13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15">
+      <c r="A15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15">
+      <c r="A16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" t="s">
         <v>15</v>
       </c>
     </row>

--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -23,7 +23,7 @@
     <t>Rok szkolny: 2025/2026</t>
   </si>
   <si>
-    <t>Okres: 27.04.2026 (pon.) - 01.05.2026 (pt.)</t>
+    <t>Okres: 27.04.2026 (pon.) - 03.05.2026 (niedz.)</t>
   </si>
   <si>
     <t>Przeniesiono z</t>
@@ -686,7 +686,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{43eac707-a56e-472c-b12e-a707f1c402fc}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{acba11b1-6bfa-497f-88b6-0baa373e9118}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -707,7 +707,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{54a5feed-29c3-4eb2-864e-f672dee7fc4f}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{6545707e-f768-4d85-818f-8775ab8b165e}">
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>

--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="107">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -134,6 +134,69 @@
     <t>j. angielski, przeniesiony na wtorek, 2 lekcja, sala 43</t>
   </si>
   <si>
+    <t>29.04.2026, 8, 14:05-14:50, sala: 04</t>
+  </si>
+  <si>
+    <t>28.04.2026, 8, 14:05-14:50, sala: 17</t>
+  </si>
+  <si>
+    <t>Wojciechowski Łukasz</t>
+  </si>
+  <si>
+    <t>3TFA|JA1</t>
+  </si>
+  <si>
+    <t>przeniesienie, j. angielski ze środy na wtorek, lekcja 8, sala 17</t>
+  </si>
+  <si>
+    <t>29.04.2026, 2, 08:50-09:35, sala: 28</t>
+  </si>
+  <si>
+    <t>29.04.2026, 2, 08:50-09:35, sala: aq1</t>
+  </si>
+  <si>
+    <t>2CA</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - dekoracje w cukiernictwie</t>
+  </si>
+  <si>
+    <t>pracownia spożywcza</t>
+  </si>
+  <si>
+    <t>29.04.2026, 3, 09:40-10:25, sala: 28</t>
+  </si>
+  <si>
+    <t>29.04.2026, 3, 09:40-10:25, sala: aq1</t>
+  </si>
+  <si>
+    <t>29.04.2026, 2, 08:50-09:35, sala: 26</t>
+  </si>
+  <si>
+    <t>29.04.2026, 4, 10:35-11:20, sala: 26</t>
+  </si>
+  <si>
+    <t>Hudziec Agnieszka</t>
+  </si>
+  <si>
+    <t>2FB</t>
+  </si>
+  <si>
+    <t>Chemia</t>
+  </si>
+  <si>
+    <t>29.04.2026, 4, 10:35-11:20, sala: 04</t>
+  </si>
+  <si>
+    <t>29.04.2026, 4, 10:35-11:20, sala: 27</t>
+  </si>
+  <si>
+    <t>1S|JA2</t>
+  </si>
+  <si>
+    <t>j. angielski, cała klasa sala 27</t>
+  </si>
+  <si>
     <t>27.04.2026, 6, 12:25-13:10, sala: 30</t>
   </si>
   <si>
@@ -143,12 +206,45 @@
     <t>Kończyńska Małgorzata</t>
   </si>
   <si>
-    <t>Rozwój kompetencji zawodowych - dekoracje w cukiernictwie</t>
-  </si>
-  <si>
     <t>p. Kończyńska, RKZ przeniesiony na środę 29 kwietnia, lekcja 5, sala 34</t>
   </si>
   <si>
+    <t>29.04.2026, 5, 11:25-12:10, sala: 04</t>
+  </si>
+  <si>
+    <t>29.04.2026, 5, 11:25-12:10, sala: 27</t>
+  </si>
+  <si>
+    <t>29.04.2026, 1, 08:00-08:45, sala: 44</t>
+  </si>
+  <si>
+    <t>29.04.2026, 6, 12:25-13:10, sala: 43</t>
+  </si>
+  <si>
+    <t>Misiąg Anna</t>
+  </si>
+  <si>
+    <t>1TH|JA1</t>
+  </si>
+  <si>
+    <t>Język niemiecki</t>
+  </si>
+  <si>
+    <t>j. niemiecki, przeniesiony na lekcję 6, sala 27</t>
+  </si>
+  <si>
+    <t>28.04.2026, 2, 08:50-09:35, sala: 26</t>
+  </si>
+  <si>
+    <t>29.04.2026, 7, 13:15-14:00, sala: 26</t>
+  </si>
+  <si>
+    <t>4TFB</t>
+  </si>
+  <si>
+    <t>chemia, p. Hudziec, przeniesiona na lekcję 7 w środę 29 kwietnia, sala 26</t>
+  </si>
+  <si>
     <t>28.04.2026, 2, 08:50-09:35, sala: 32</t>
   </si>
   <si>
@@ -161,33 +257,27 @@
     <t>j. angielski przeniesiony na środę, 8 lekcja, sala 32</t>
   </si>
   <si>
+    <t>29.04.2026, 9, 14:55-15:40, sala: 4</t>
+  </si>
+  <si>
+    <t>29.04.2026, 8, 14:05-14:50, sala: 4</t>
+  </si>
+  <si>
+    <t>Kopij Marcin</t>
+  </si>
+  <si>
+    <t>Edukacja obywatelska</t>
+  </si>
+  <si>
     <t>30.04.2026, 8, 14:05-14:50, sala: 4</t>
   </si>
   <si>
-    <t>29.04.2026, 8, 14:05-14:50, sala: 4</t>
-  </si>
-  <si>
     <t>Kruk Marcin</t>
   </si>
   <si>
     <t>1FA</t>
   </si>
   <si>
-    <t>Chemia</t>
-  </si>
-  <si>
-    <t>29.04.2026, 9, 14:55-15:40, sala: 4</t>
-  </si>
-  <si>
-    <t>29.04.2026, 9, 14:55-15:40, sala: 2</t>
-  </si>
-  <si>
-    <t>Kopij Marcin</t>
-  </si>
-  <si>
-    <t>Edukacja obywatelska</t>
-  </si>
-  <si>
     <t>30.04.2026, 9, 14:55-15:40, sala: 4</t>
   </si>
   <si>
@@ -237,6 +327,18 @@
   </si>
   <si>
     <t>29.04.2026, 13, 18:15-19:00, sala: 4</t>
+  </si>
+  <si>
+    <t>30.04.2026, 8, 14:05-14:50, sala: 17</t>
+  </si>
+  <si>
+    <t>30.04.2026, 6, 12:25-13:10, sala: 17</t>
+  </si>
+  <si>
+    <t>Filusz Marzena</t>
+  </si>
+  <si>
+    <t>3TFB</t>
   </si>
 </sst>
 </file>
@@ -686,7 +788,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{acba11b1-6bfa-497f-88b6-0baa373e9118}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{672cc3c3-e846-480e-af9f-8d3520c029fc}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -707,12 +809,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{6545707e-f768-4d85-818f-8775ab8b165e}">
-  <dimension ref="A1:G16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{24782aca-43d9-44dd-9df4-a3b0410c7ef2}">
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="31.4285714285714" customWidth="1"/>
+    <col min="2" max="2" width="31.8571428571429" customWidth="1"/>
     <col min="3" max="3" width="22.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
@@ -872,10 +974,10 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G7" t="s">
         <v>42</v>
@@ -889,7 +991,7 @@
         <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
@@ -898,53 +1000,53 @@
         <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="G8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15">
       <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" t="s">
         <v>47</v>
-      </c>
-      <c r="B9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15">
       <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
         <v>52</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
         <v>53</v>
       </c>
-      <c r="C10" t="s">
+      <c r="F10" t="s">
         <v>54</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
@@ -952,139 +1054,346 @@
     </row>
     <row r="11" spans="1:7" ht="15">
       <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" t="s">
         <v>56</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
         <v>57</v>
       </c>
-      <c r="C11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" t="s">
         <v>58</v>
-      </c>
-      <c r="F11" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15">
       <c r="A12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" t="s">
         <v>60</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>61</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" t="s">
         <v>62</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
       </c>
       <c r="E13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" t="s">
         <v>58</v>
-      </c>
-      <c r="F13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15">
       <c r="A14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" t="s">
         <v>67</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
         <v>68</v>
       </c>
-      <c r="C14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" t="s">
-        <v>58</v>
-      </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="F16" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="G16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15">
+      <c r="A17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15">
+      <c r="A18" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15">
+      <c r="A19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15">
+      <c r="A20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="s">
+        <v>93</v>
+      </c>
+      <c r="F20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15">
+      <c r="A21" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" t="s">
+        <v>88</v>
+      </c>
+      <c r="F21" t="s">
+        <v>89</v>
+      </c>
+      <c r="G21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15">
+      <c r="A22" t="s">
+        <v>97</v>
+      </c>
+      <c r="B22" t="s">
+        <v>98</v>
+      </c>
+      <c r="C22" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" t="s">
+        <v>88</v>
+      </c>
+      <c r="F22" t="s">
+        <v>89</v>
+      </c>
+      <c r="G22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15">
+      <c r="A23" t="s">
+        <v>99</v>
+      </c>
+      <c r="B23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
+        <v>88</v>
+      </c>
+      <c r="F23" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15">
+      <c r="A24" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15">
+      <c r="A25" t="s">
+        <v>103</v>
+      </c>
+      <c r="B25" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" t="s">
+        <v>105</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
+        <v>106</v>
+      </c>
+      <c r="F25" t="s">
+        <v>94</v>
+      </c>
+      <c r="G25" t="s">
         <v>15</v>
       </c>
     </row>

--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -788,7 +788,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{672cc3c3-e846-480e-af9f-8d3520c029fc}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e10e36b7-de55-402a-96de-b6d1a5806d77}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -809,7 +809,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{24782aca-43d9-44dd-9df4-a3b0410c7ef2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d05c14ce-81bb-4a79-bdbc-ab60883d645e}">
   <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>

--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -788,7 +788,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e10e36b7-de55-402a-96de-b6d1a5806d77}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ea5ac5a1-edc8-4072-9c57-bea1305d823a}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -809,7 +809,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d05c14ce-81bb-4a79-bdbc-ab60883d645e}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8b0b1aee-5a5d-4bd7-851b-4ac42956fc68}">
   <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>

--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="148">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -329,6 +329,69 @@
     <t>29.04.2026, 13, 18:15-19:00, sala: 4</t>
   </si>
   <si>
+    <t>30.04.2026, 4, 10:35-11:20, sala: 17</t>
+  </si>
+  <si>
+    <t>30.04.2026, 4, 10:35-11:20, sala: 31</t>
+  </si>
+  <si>
+    <t>Fiodorów Małgorzata</t>
+  </si>
+  <si>
+    <t>1TH|JA2</t>
+  </si>
+  <si>
+    <t>30.04.2026, 4, 10:35-11:20, sala: 22</t>
+  </si>
+  <si>
+    <t>30.04.2026, 4, 10:35-11:20, sala: 34</t>
+  </si>
+  <si>
+    <t>Ulanowska Magdalena</t>
+  </si>
+  <si>
+    <t>1TFA</t>
+  </si>
+  <si>
+    <t>30.04.2026, 5, 11:25-12:10, sala: 17</t>
+  </si>
+  <si>
+    <t>30.04.2026, 5, 11:25-12:10, sala: 31</t>
+  </si>
+  <si>
+    <t>1WA|JN1</t>
+  </si>
+  <si>
+    <t>30.04.2026, 5, 11:25-12:10, sala: 22</t>
+  </si>
+  <si>
+    <t>30.04.2026, 5, 11:25-12:10, sala: 34</t>
+  </si>
+  <si>
+    <t>30.04.2026, 5, 11:25-12:10, sala: 04</t>
+  </si>
+  <si>
+    <t>30.04.2026, 5, 11:25-12:10, sala: 2</t>
+  </si>
+  <si>
+    <t>1FC|JA2</t>
+  </si>
+  <si>
+    <t>30.04.2026, 6, 12:25-13:10, sala: 5</t>
+  </si>
+  <si>
+    <t>30.04.2026, 6, 12:25-13:10, sala: 31</t>
+  </si>
+  <si>
+    <t>Biczysko Wojciech</t>
+  </si>
+  <si>
+    <t>2WB</t>
+  </si>
+  <si>
+    <t>Fizyka</t>
+  </si>
+  <si>
     <t>30.04.2026, 8, 14:05-14:50, sala: 17</t>
   </si>
   <si>
@@ -339,6 +402,66 @@
   </si>
   <si>
     <t>3TFB</t>
+  </si>
+  <si>
+    <t>30.04.2026, 6, 12:25-13:10, sala: 04</t>
+  </si>
+  <si>
+    <t>30.04.2026, 6, 12:25-13:10, sala: 2</t>
+  </si>
+  <si>
+    <t>1FA|JA2</t>
+  </si>
+  <si>
+    <t>30.04.2026, 6, 12:25-13:10, sala: 3</t>
+  </si>
+  <si>
+    <t>Wójcik Kamil</t>
+  </si>
+  <si>
+    <t>1WA</t>
+  </si>
+  <si>
+    <t>30.04.2026, 6, 12:25-13:10, sala: 19</t>
+  </si>
+  <si>
+    <t>30.04.2026, 6, 12:25-13:10, sala: 32</t>
+  </si>
+  <si>
+    <t>Zaleska Magdalena</t>
+  </si>
+  <si>
+    <t>Historia</t>
+  </si>
+  <si>
+    <t>30.04.2026, 7, 13:15-14:00, sala: 5</t>
+  </si>
+  <si>
+    <t>30.04.2026, 7, 13:15-14:00, sala: 31</t>
+  </si>
+  <si>
+    <t>30.04.2026, 7, 13:15-14:00, sala: 22</t>
+  </si>
+  <si>
+    <t>30.04.2026, 7, 13:15-14:00, sala: 27</t>
+  </si>
+  <si>
+    <t>4TH</t>
+  </si>
+  <si>
+    <t>30.04.2026, 7, 13:15-14:00, sala: 19</t>
+  </si>
+  <si>
+    <t>30.04.2026, 7, 13:15-14:00, sala: 32</t>
+  </si>
+  <si>
+    <t>2TFA</t>
+  </si>
+  <si>
+    <t>30.04.2026, 8, 14:05-14:50, sala: 22</t>
+  </si>
+  <si>
+    <t>30.04.2026, 8, 14:05-14:50, sala: 26</t>
   </si>
 </sst>
 </file>
@@ -788,7 +911,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ea5ac5a1-edc8-4072-9c57-bea1305d823a}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{13b9fc4a-8f40-41d9-a2d5-af5443ef142e}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -809,8 +932,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8b0b1aee-5a5d-4bd7-851b-4ac42956fc68}">
-  <dimension ref="A1:G25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{cc969711-1cdb-4c49-ad11-e51b4691bb81}">
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.7142857142857" customWidth="1"/>
@@ -1391,9 +1514,308 @@
         <v>106</v>
       </c>
       <c r="F25" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15">
+      <c r="A26" t="s">
+        <v>107</v>
+      </c>
+      <c r="B26" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" t="s">
+        <v>110</v>
+      </c>
+      <c r="F26" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15">
+      <c r="A27" t="s">
+        <v>111</v>
+      </c>
+      <c r="B27" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27" t="s">
+        <v>105</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
+        <v>113</v>
+      </c>
+      <c r="F27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15">
+      <c r="A28" t="s">
+        <v>114</v>
+      </c>
+      <c r="B28" t="s">
+        <v>115</v>
+      </c>
+      <c r="C28" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" t="s">
+        <v>110</v>
+      </c>
+      <c r="F28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15">
+      <c r="A29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B29" t="s">
+        <v>117</v>
+      </c>
+      <c r="C29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" t="s">
+        <v>118</v>
+      </c>
+      <c r="F29" t="s">
+        <v>31</v>
+      </c>
+      <c r="G29" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15">
+      <c r="A30" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30" t="s">
+        <v>120</v>
+      </c>
+      <c r="C30" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" t="s">
+        <v>122</v>
+      </c>
+      <c r="F30" t="s">
+        <v>123</v>
+      </c>
+      <c r="G30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15">
+      <c r="A31" t="s">
+        <v>124</v>
+      </c>
+      <c r="B31" t="s">
+        <v>125</v>
+      </c>
+      <c r="C31" t="s">
+        <v>126</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" t="s">
+        <v>127</v>
+      </c>
+      <c r="F31" t="s">
         <v>94</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15">
+      <c r="A32" t="s">
+        <v>128</v>
+      </c>
+      <c r="B32" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" t="s">
+        <v>130</v>
+      </c>
+      <c r="F32" t="s">
+        <v>31</v>
+      </c>
+      <c r="G32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15">
+      <c r="A33" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" t="s">
+        <v>131</v>
+      </c>
+      <c r="C33" t="s">
+        <v>132</v>
+      </c>
+      <c r="D33" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" t="s">
+        <v>133</v>
+      </c>
+      <c r="F33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15">
+      <c r="A34" t="s">
+        <v>134</v>
+      </c>
+      <c r="B34" t="s">
+        <v>135</v>
+      </c>
+      <c r="C34" t="s">
+        <v>136</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" t="s">
+        <v>30</v>
+      </c>
+      <c r="F34" t="s">
+        <v>137</v>
+      </c>
+      <c r="G34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15">
+      <c r="A35" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" t="s">
+        <v>121</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" t="s">
+        <v>133</v>
+      </c>
+      <c r="F35" t="s">
+        <v>123</v>
+      </c>
+      <c r="G35" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15">
+      <c r="A36" t="s">
+        <v>140</v>
+      </c>
+      <c r="B36" t="s">
+        <v>141</v>
+      </c>
+      <c r="C36" t="s">
+        <v>109</v>
+      </c>
+      <c r="D36" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" t="s">
+        <v>142</v>
+      </c>
+      <c r="F36" t="s">
+        <v>25</v>
+      </c>
+      <c r="G36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15">
+      <c r="A37" t="s">
+        <v>143</v>
+      </c>
+      <c r="B37" t="s">
+        <v>144</v>
+      </c>
+      <c r="C37" t="s">
+        <v>136</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" t="s">
+        <v>145</v>
+      </c>
+      <c r="F37" t="s">
+        <v>137</v>
+      </c>
+      <c r="G37" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15">
+      <c r="A38" t="s">
+        <v>146</v>
+      </c>
+      <c r="B38" t="s">
+        <v>147</v>
+      </c>
+      <c r="C38" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" t="s">
+        <v>133</v>
+      </c>
+      <c r="F38" t="s">
+        <v>25</v>
+      </c>
+      <c r="G38" t="s">
         <v>15</v>
       </c>
     </row>

--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
   <si>
     <t>Rok szkolny: 2026/2027</t>
   </si>
   <si>
-    <t>Okres: 01.09.2026 (wt.) - 06.09.2026 (niedz.)</t>
+    <t>Okres: 07.09.2026 (pon.) - 07.09.2026 (pon.)</t>
   </si>
   <si>
     <t>Przeniesiono z</t>
@@ -47,19 +47,19 @@
     <t>Uwagi</t>
   </si>
   <si>
-    <t>02.09.2026, 4, 10:35-11:20, sala: 05</t>
-  </si>
-  <si>
-    <t>02.09.2026, 4, 10:35-11:20, sala: 33</t>
-  </si>
-  <si>
-    <t>Staliś Donata</t>
+    <t>07.09.2026, 1, 08:00-08:45, sala: 05</t>
+  </si>
+  <si>
+    <t>07.09.2026, 1, 08:00-08:45, sala: 2</t>
+  </si>
+  <si>
+    <t>Karczmarz Aleksandra</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4TH|gr1</t>
+    <t>2FC</t>
   </si>
   <si>
     <t>Język angielski</t>
@@ -68,19 +68,49 @@
     <t/>
   </si>
   <si>
-    <t>02.09.2026, 5, 11:25-12:10, sala: 05</t>
-  </si>
-  <si>
-    <t>02.09.2026, 5, 11:25-12:10, sala: 27</t>
-  </si>
-  <si>
-    <t>02.09.2026, 6, 12:25-13:10, sala: 05</t>
-  </si>
-  <si>
-    <t>02.09.2026, 6, 12:25-13:10, sala: 27</t>
-  </si>
-  <si>
-    <t>1FA|gr1</t>
+    <t>07.09.2026, 2, 08:50-09:35, sala: 05</t>
+  </si>
+  <si>
+    <t>07.09.2026, 2, 08:50-09:35, sala: 2</t>
+  </si>
+  <si>
+    <t>2K|gr1</t>
+  </si>
+  <si>
+    <t>07.09.2026, 3, 09:40-10:25, sala: 05</t>
+  </si>
+  <si>
+    <t>07.09.2026, 3, 09:40-10:25, sala: 4</t>
+  </si>
+  <si>
+    <t>2FA</t>
+  </si>
+  <si>
+    <t>07.09.2026, 4, 10:35-11:20, sala: 05</t>
+  </si>
+  <si>
+    <t>07.09.2026, 4, 10:35-11:20, sala: 3</t>
+  </si>
+  <si>
+    <t>2CA</t>
+  </si>
+  <si>
+    <t>07.09.2026, 5, 11:25-12:10, sala: 05</t>
+  </si>
+  <si>
+    <t>07.09.2026, 5, 11:25-12:10, sala: 4</t>
+  </si>
+  <si>
+    <t>2S</t>
+  </si>
+  <si>
+    <t>07.09.2026, 6, 12:25-13:10, sala: 05</t>
+  </si>
+  <si>
+    <t>07.09.2026, 6, 12:25-13:10, sala: 4</t>
+  </si>
+  <si>
+    <t>1TFH|gr1</t>
   </si>
 </sst>
 </file>
@@ -530,7 +560,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{61436d90-ab86-4c99-8a19-5e782c290510}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{40c80021-437c-48f1-8772-fba310692bb5}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -551,12 +581,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{3e1545c4-ab5e-4fb3-a21f-7a58f3868f92}">
-  <dimension ref="A1:G4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{438b0631-8cea-4b63-9478-fb1b3490335a}">
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="30.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="19.4285714285714" customWidth="1"/>
+    <col min="1" max="1" width="30.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="29.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="20.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
     <col min="6" max="6" width="14.1428571428571" customWidth="1"/>
@@ -623,7 +654,7 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
@@ -634,10 +665,10 @@
     </row>
     <row r="4" spans="1:7" ht="15">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
@@ -646,12 +677,81 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
       </c>
       <c r="G4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
         <v>15</v>
       </c>
     </row>

--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -23,7 +23,7 @@
     <t>Rok szkolny: 2026/2027</t>
   </si>
   <si>
-    <t>Okres: 07.09.2026 (pon.) - 07.09.2026 (pon.)</t>
+    <t>Okres: 07.09.2026 (pon.) - 13.09.2026 (niedz.)</t>
   </si>
   <si>
     <t>Przeniesiono z</t>
@@ -560,7 +560,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{40c80021-437c-48f1-8772-fba310692bb5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d06da384-35e2-420d-9596-5e91925e8e1b}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -581,7 +581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{438b0631-8cea-4b63-9478-fb1b3490335a}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d8777945-3938-46dc-a1c8-406a9a94c65e}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>

--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>Rok szkolny: 2026/2027</t>
   </si>
   <si>
-    <t>Okres: 07.09.2026 (pon.) - 07.09.2026 (pon.)</t>
+    <t>Okres: 07.09.2026 (pon.) - 13.09.2026 (niedz.)</t>
   </si>
   <si>
     <t>Przeniesiono z</t>
@@ -111,6 +111,189 @@
   </si>
   <si>
     <t>1TFH|gr1</t>
+  </si>
+  <si>
+    <t>08.09.2026, 7, 13:15-14:00, sala: 05</t>
+  </si>
+  <si>
+    <t>08.09.2026, 7, 13:15-14:00, sala: 18</t>
+  </si>
+  <si>
+    <t>Galert Anna</t>
+  </si>
+  <si>
+    <t>1FB</t>
+  </si>
+  <si>
+    <t>Zajęcia z wychowawcą</t>
+  </si>
+  <si>
+    <t>08.09.2026, 8, 14:05-14:50, sala: 05</t>
+  </si>
+  <si>
+    <t>08.09.2026, 8, 14:05-14:50, sala: 18</t>
+  </si>
+  <si>
+    <t>1CA|gr1</t>
+  </si>
+  <si>
+    <t>09.09.2026, 3, 09:40-10:25, sala: 05</t>
+  </si>
+  <si>
+    <t>09.09.2026, 3, 09:40-10:25, sala: 23</t>
+  </si>
+  <si>
+    <t>Granatowska Mariola</t>
+  </si>
+  <si>
+    <t>2K|gr2</t>
+  </si>
+  <si>
+    <t>09.09.2026, 4, 10:35-11:20, sala: 05</t>
+  </si>
+  <si>
+    <t>09.09.2026, 4, 10:35-11:20, sala: 2</t>
+  </si>
+  <si>
+    <t>4TH|gr2</t>
+  </si>
+  <si>
+    <t>09.09.2026, 5, 11:25-12:10, sala: 05</t>
+  </si>
+  <si>
+    <t>09.09.2026, 5, 11:25-12:10, sala: bib</t>
+  </si>
+  <si>
+    <t>09.09.2026, 6, 12:25-13:10, sala: 05</t>
+  </si>
+  <si>
+    <t>09.09.2026, 6, 12:25-13:10, sala: 2</t>
+  </si>
+  <si>
+    <t>3TFA</t>
+  </si>
+  <si>
+    <t>09.09.2026, 7, 13:15-14:00, sala: 05</t>
+  </si>
+  <si>
+    <t>09.09.2026, 7, 13:15-14:00, sala: 2</t>
+  </si>
+  <si>
+    <t>2CB</t>
+  </si>
+  <si>
+    <t>10.09.2026, 3, 09:40-10:25, sala: 05</t>
+  </si>
+  <si>
+    <t>10.09.2026, 3, 09:40-10:25, sala: 3</t>
+  </si>
+  <si>
+    <t>1FA|gr2</t>
+  </si>
+  <si>
+    <t>10.09.2026, 4, 10:35-11:20, sala: 05</t>
+  </si>
+  <si>
+    <t>10.09.2026, 4, 10:35-11:20, sala: 3</t>
+  </si>
+  <si>
+    <t>1K|gr1</t>
+  </si>
+  <si>
+    <t>10.09.2026, 5, 11:25-12:10, sala: 05</t>
+  </si>
+  <si>
+    <t>10.09.2026, 5, 11:25-12:10, sala: 3</t>
+  </si>
+  <si>
+    <t>1FC|gr1</t>
+  </si>
+  <si>
+    <t>10.09.2026, 6, 12:25-13:10, sala: 05</t>
+  </si>
+  <si>
+    <t>10.09.2026, 6, 12:25-13:10, sala: 3</t>
+  </si>
+  <si>
+    <t>1TFA|gr2</t>
+  </si>
+  <si>
+    <t>10.09.2026, 7, 13:15-14:00, sala: 05</t>
+  </si>
+  <si>
+    <t>10.09.2026, 7, 13:15-14:00, sala: 5</t>
+  </si>
+  <si>
+    <t>1S|gr2</t>
+  </si>
+  <si>
+    <t>11.09.2026, 2, 08:50-09:35, sala: 05</t>
+  </si>
+  <si>
+    <t>11.09.2026, 2, 08:50-09:35, sala: 18</t>
+  </si>
+  <si>
+    <t>4TFA</t>
+  </si>
+  <si>
+    <t>11.09.2026, 3, 09:40-10:25, sala: 05</t>
+  </si>
+  <si>
+    <t>11.09.2026, 3, 09:40-10:25, sala: 17</t>
+  </si>
+  <si>
+    <t>11.09.2026, 4, 10:35-11:20, sala: 05</t>
+  </si>
+  <si>
+    <t>11.09.2026, 4, 10:35-11:20, sala: 17</t>
+  </si>
+  <si>
+    <t>11.09.2026, 5, 11:25-12:10, sala: 05</t>
+  </si>
+  <si>
+    <t>11.09.2026, 5, 11:25-12:10, sala: 40</t>
+  </si>
+  <si>
+    <t>1TFB|gr1</t>
+  </si>
+  <si>
+    <t>11.09.2026, 6, 12:25-13:10, sala: 05</t>
+  </si>
+  <si>
+    <t>11.09.2026, 6, 12:25-13:10, sala: 40</t>
+  </si>
+  <si>
+    <t>3TFB|gr1</t>
+  </si>
+  <si>
+    <t>11.09.2026, 7, 13:15-14:00, sala: 05</t>
+  </si>
+  <si>
+    <t>11.09.2026, 7, 13:15-14:00, sala: 41</t>
+  </si>
+  <si>
+    <t>1CB|gr1</t>
+  </si>
+  <si>
+    <t>11.09.2026, 8, 14:05-14:50, sala: 05</t>
+  </si>
+  <si>
+    <t>11.09.2026, 8, 14:05-14:50, sala: 40</t>
+  </si>
+  <si>
+    <t>11.09.2026, 9, 14:55-15:40, sala: 05</t>
+  </si>
+  <si>
+    <t>11.09.2026, 9, 14:55-15:40, sala: 40</t>
+  </si>
+  <si>
+    <t>11.09.2026, 10, 15:45-16:30, sala: 05</t>
+  </si>
+  <si>
+    <t>11.09.2026, 10, 15:45-16:30, sala: 40</t>
+  </si>
+  <si>
+    <t>1FB|gr1</t>
   </si>
 </sst>
 </file>
@@ -560,7 +743,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{40c80021-437c-48f1-8772-fba310692bb5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{5d64cdcb-b1f1-43c1-bc68-85d26f780813}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -581,16 +764,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{438b0631-8cea-4b63-9478-fb1b3490335a}">
-  <dimension ref="A1:G7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{b07396a0-dd9b-4d91-86bc-f0cb21bca76a}">
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="29.7142857142857" customWidth="1"/>
+    <col min="1" max="2" width="31.7142857142857" customWidth="1"/>
     <col min="3" max="3" width="20.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="14.1428571428571" customWidth="1"/>
+    <col min="6" max="6" width="20.7142857142857" customWidth="1"/>
     <col min="7" max="7" width="9.28571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -755,6 +937,489 @@
         <v>15</v>
       </c>
     </row>
+    <row r="8" spans="1:7" ht="15">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15">
+      <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15">
+      <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15">
+      <c r="A14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15">
+      <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15">
+      <c r="A16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15">
+      <c r="A17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15">
+      <c r="A18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15">
+      <c r="A19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15">
+      <c r="A20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15">
+      <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" t="s">
+        <v>71</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15">
+      <c r="A22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15">
+      <c r="A23" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
+        <v>78</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15">
+      <c r="A24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15">
+      <c r="A25" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
+        <v>84</v>
+      </c>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15">
+      <c r="A26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" t="s">
+        <v>59</v>
+      </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15">
+      <c r="A27" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
+        <v>62</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15">
+      <c r="A28" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" t="s">
+        <v>91</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>Rok szkolny: 2026/2027</t>
   </si>
@@ -111,6 +111,189 @@
   </si>
   <si>
     <t>1TFH|gr1</t>
+  </si>
+  <si>
+    <t>08.09.2026, 7, 13:15-14:00, sala: 05</t>
+  </si>
+  <si>
+    <t>08.09.2026, 7, 13:15-14:00, sala: 18</t>
+  </si>
+  <si>
+    <t>Galert Anna</t>
+  </si>
+  <si>
+    <t>1FB</t>
+  </si>
+  <si>
+    <t>Zajęcia z wychowawcą</t>
+  </si>
+  <si>
+    <t>08.09.2026, 8, 14:05-14:50, sala: 05</t>
+  </si>
+  <si>
+    <t>08.09.2026, 8, 14:05-14:50, sala: 18</t>
+  </si>
+  <si>
+    <t>1CA|gr1</t>
+  </si>
+  <si>
+    <t>09.09.2026, 3, 09:40-10:25, sala: 05</t>
+  </si>
+  <si>
+    <t>09.09.2026, 3, 09:40-10:25, sala: 23</t>
+  </si>
+  <si>
+    <t>Granatowska Mariola</t>
+  </si>
+  <si>
+    <t>2K|gr2</t>
+  </si>
+  <si>
+    <t>09.09.2026, 4, 10:35-11:20, sala: 05</t>
+  </si>
+  <si>
+    <t>09.09.2026, 4, 10:35-11:20, sala: 2</t>
+  </si>
+  <si>
+    <t>4TH|gr2</t>
+  </si>
+  <si>
+    <t>09.09.2026, 5, 11:25-12:10, sala: 05</t>
+  </si>
+  <si>
+    <t>09.09.2026, 5, 11:25-12:10, sala: bib</t>
+  </si>
+  <si>
+    <t>09.09.2026, 6, 12:25-13:10, sala: 05</t>
+  </si>
+  <si>
+    <t>09.09.2026, 6, 12:25-13:10, sala: 2</t>
+  </si>
+  <si>
+    <t>3TFA</t>
+  </si>
+  <si>
+    <t>09.09.2026, 7, 13:15-14:00, sala: 05</t>
+  </si>
+  <si>
+    <t>09.09.2026, 7, 13:15-14:00, sala: 2</t>
+  </si>
+  <si>
+    <t>2CB</t>
+  </si>
+  <si>
+    <t>10.09.2026, 3, 09:40-10:25, sala: 05</t>
+  </si>
+  <si>
+    <t>10.09.2026, 3, 09:40-10:25, sala: 3</t>
+  </si>
+  <si>
+    <t>1FA|gr2</t>
+  </si>
+  <si>
+    <t>10.09.2026, 4, 10:35-11:20, sala: 05</t>
+  </si>
+  <si>
+    <t>10.09.2026, 4, 10:35-11:20, sala: 3</t>
+  </si>
+  <si>
+    <t>1K|gr1</t>
+  </si>
+  <si>
+    <t>10.09.2026, 5, 11:25-12:10, sala: 05</t>
+  </si>
+  <si>
+    <t>10.09.2026, 5, 11:25-12:10, sala: 3</t>
+  </si>
+  <si>
+    <t>1FC|gr1</t>
+  </si>
+  <si>
+    <t>10.09.2026, 6, 12:25-13:10, sala: 05</t>
+  </si>
+  <si>
+    <t>10.09.2026, 6, 12:25-13:10, sala: 3</t>
+  </si>
+  <si>
+    <t>1TFA|gr2</t>
+  </si>
+  <si>
+    <t>10.09.2026, 7, 13:15-14:00, sala: 05</t>
+  </si>
+  <si>
+    <t>10.09.2026, 7, 13:15-14:00, sala: 5</t>
+  </si>
+  <si>
+    <t>1S|gr2</t>
+  </si>
+  <si>
+    <t>11.09.2026, 2, 08:50-09:35, sala: 05</t>
+  </si>
+  <si>
+    <t>11.09.2026, 2, 08:50-09:35, sala: 18</t>
+  </si>
+  <si>
+    <t>4TFA</t>
+  </si>
+  <si>
+    <t>11.09.2026, 3, 09:40-10:25, sala: 05</t>
+  </si>
+  <si>
+    <t>11.09.2026, 3, 09:40-10:25, sala: 17</t>
+  </si>
+  <si>
+    <t>11.09.2026, 4, 10:35-11:20, sala: 05</t>
+  </si>
+  <si>
+    <t>11.09.2026, 4, 10:35-11:20, sala: 17</t>
+  </si>
+  <si>
+    <t>11.09.2026, 5, 11:25-12:10, sala: 05</t>
+  </si>
+  <si>
+    <t>11.09.2026, 5, 11:25-12:10, sala: 40</t>
+  </si>
+  <si>
+    <t>1TFB|gr1</t>
+  </si>
+  <si>
+    <t>11.09.2026, 6, 12:25-13:10, sala: 05</t>
+  </si>
+  <si>
+    <t>11.09.2026, 6, 12:25-13:10, sala: 40</t>
+  </si>
+  <si>
+    <t>3TFB|gr1</t>
+  </si>
+  <si>
+    <t>11.09.2026, 7, 13:15-14:00, sala: 05</t>
+  </si>
+  <si>
+    <t>11.09.2026, 7, 13:15-14:00, sala: 41</t>
+  </si>
+  <si>
+    <t>1CB|gr1</t>
+  </si>
+  <si>
+    <t>11.09.2026, 8, 14:05-14:50, sala: 05</t>
+  </si>
+  <si>
+    <t>11.09.2026, 8, 14:05-14:50, sala: 40</t>
+  </si>
+  <si>
+    <t>11.09.2026, 9, 14:55-15:40, sala: 05</t>
+  </si>
+  <si>
+    <t>11.09.2026, 9, 14:55-15:40, sala: 40</t>
+  </si>
+  <si>
+    <t>11.09.2026, 10, 15:45-16:30, sala: 05</t>
+  </si>
+  <si>
+    <t>11.09.2026, 10, 15:45-16:30, sala: 40</t>
+  </si>
+  <si>
+    <t>1FB|gr1</t>
   </si>
 </sst>
 </file>
@@ -560,7 +743,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d06da384-35e2-420d-9596-5e91925e8e1b}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{5d64cdcb-b1f1-43c1-bc68-85d26f780813}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -581,16 +764,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d8777945-3938-46dc-a1c8-406a9a94c65e}">
-  <dimension ref="A1:G7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{b07396a0-dd9b-4d91-86bc-f0cb21bca76a}">
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="29.7142857142857" customWidth="1"/>
+    <col min="1" max="2" width="31.7142857142857" customWidth="1"/>
     <col min="3" max="3" width="20.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="32.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="14.1428571428571" customWidth="1"/>
+    <col min="6" max="6" width="20.7142857142857" customWidth="1"/>
     <col min="7" max="7" width="9.28571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -755,6 +937,489 @@
         <v>15</v>
       </c>
     </row>
+    <row r="8" spans="1:7" ht="15">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15">
+      <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15">
+      <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15">
+      <c r="A14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15">
+      <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15">
+      <c r="A16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15">
+      <c r="A17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15">
+      <c r="A18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15">
+      <c r="A19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15">
+      <c r="A20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15">
+      <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" t="s">
+        <v>71</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15">
+      <c r="A22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15">
+      <c r="A23" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
+        <v>78</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15">
+      <c r="A24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15">
+      <c r="A25" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
+        <v>84</v>
+      </c>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15">
+      <c r="A26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" t="s">
+        <v>59</v>
+      </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15">
+      <c r="A27" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
+        <v>62</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15">
+      <c r="A28" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" t="s">
+        <v>91</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/InformacjeOPrzeniesieniach.xlsx
+++ b/InformacjeOPrzeniesieniach.xlsx
@@ -743,7 +743,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{5d64cdcb-b1f1-43c1-bc68-85d26f780813}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{569de468-be56-4b9c-b8e8-5f25a1b9f03e}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -764,7 +764,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{b07396a0-dd9b-4d91-86bc-f0cb21bca76a}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{a951eef4-1939-47f3-9368-c1732cb7c658}">
   <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
